--- a/output/graficos_nacionales/plot_nacional_i_ingr_mean_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_i_ingr_mean_a_2021.xlsx
@@ -15267,7 +15267,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Ingreso de la población en edad de trabajar</t>
+          <t>Por comunas</t>
         </is>
       </c>
     </row>

--- a/output/graficos_nacionales/plot_nacional_i_ingr_mean_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_i_ingr_mean_a_2021.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="690">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="693">
   <si>
     <t xml:space="preserve">year</t>
   </si>
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Macrozona Austral</t>
   </si>
   <si>
-    <t xml:space="preserve">value</t>
+    <t xml:space="preserve">Valor ($)</t>
   </si>
   <si>
     <t xml:space="preserve">12101</t>
@@ -2050,7 +2050,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 22:15</t>
+    <t xml:space="preserve">2026-07-30 15:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -2062,16 +2062,25 @@
     <t xml:space="preserve">Imagen asociada</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t xml:space="preserve">plot_nacional_i_ingr_mean_a_2021.png</t>
   </si>
   <si>
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
+    <t xml:space="preserve">Ingreso de la población en edad de trabajar</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unidad territorial</t>
   </si>
   <si>
+    <t xml:space="preserve">Comuna (vista nacional macrozonal)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Año</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021</t>
   </si>
   <si>
     <t xml:space="preserve">variable</t>
@@ -12852,23 +12861,23 @@
         <v>682</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
     </row>
   </sheetData>
@@ -12883,28 +12892,28 @@
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="15.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="11.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="10.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="13.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>15</v>
@@ -12913,7 +12922,7 @@
         <v>2021</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_nacionales/plot_nacional_i_ingr_mean_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_i_ingr_mean_a_2021.xlsx
@@ -2050,7 +2050,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30 15:20</t>
+    <t xml:space="preserve">2026-09-07 13:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_i_ingr_mean_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_i_ingr_mean_a_2021.xlsx
@@ -2050,7 +2050,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 13:02</t>
+    <t xml:space="preserve">2026-09-08 10:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
